--- a/trunk/plan/excel/英雄属性表.xlsx
+++ b/trunk/plan/excel/英雄属性表.xlsx
@@ -26,8 +26,172 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+生命</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+法力</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+攻击强度</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+法术强度</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+护甲</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+法术抗性</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+暴击率</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>ID</t>
   </si>
@@ -35,10 +199,34 @@
     <t>Name</t>
   </si>
   <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>AttackPower</t>
+  </si>
+  <si>
+    <t>MagicPower</t>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>MagicResist</t>
+  </si>
+  <si>
+    <t>CritRate</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>number</t>
   </si>
   <si>
     <t>神力恩泽</t>
@@ -84,7 +272,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,6 +423,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1033,119 +1232,165 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
+    <col min="5" max="5" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
+    <col min="8" max="8" width="12.625" customWidth="1"/>
     <col min="10" max="10" width="10.375" customWidth="1"/>
     <col min="11" max="12" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/trunk/plan/excel/英雄属性表.xlsx
+++ b/trunk/plan/excel/英雄属性表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25185" windowHeight="7995"/>
+    <workbookView windowHeight="8130"/>
   </bookViews>
   <sheets>
     <sheet name="HeroAttrCFG" sheetId="1" r:id="rId1"/>
@@ -160,7 +160,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-法术抗性</t>
+护盾</t>
         </r>
       </text>
     </comment>
@@ -182,7 +182,227 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+法术抗性</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 暴击率</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+暴击伤害</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+闪避率</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+命中率</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+力量</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+敏捷</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+智力</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+精神</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+耐力</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+智慧</t>
         </r>
       </text>
     </comment>
@@ -191,7 +411,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
   <si>
     <t>ID</t>
   </si>
@@ -214,12 +434,42 @@
     <t>Armor</t>
   </si>
   <si>
+    <t>Shield</t>
+  </si>
+  <si>
     <t>MagicResist</t>
   </si>
   <si>
     <t>CritRate</t>
   </si>
   <si>
+    <t>CRIT_DMG</t>
+  </si>
+  <si>
+    <t>DODGE_RATE</t>
+  </si>
+  <si>
+    <t>HIT_RATE</t>
+  </si>
+  <si>
+    <t>STR</t>
+  </si>
+  <si>
+    <t>AGI</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>SPI</t>
+  </si>
+  <si>
+    <t>END</t>
+  </si>
+  <si>
+    <t>WIS</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -260,6 +510,9 @@
   </si>
   <si>
     <t>星辰之佑11</t>
+  </si>
+  <si>
+    <t>外星人</t>
   </si>
 </sst>
 </file>
@@ -1232,17 +1485,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="5" max="5" width="12.625" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
-    <col min="8" max="8" width="12.625" customWidth="1"/>
-    <col min="10" max="10" width="10.375" customWidth="1"/>
-    <col min="11" max="12" width="11.5" customWidth="1"/>
+    <col min="9" max="9" width="12.625" customWidth="1"/>
+    <col min="11" max="11" width="10.375" customWidth="1"/>
+    <col min="12" max="13" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1270,122 +1523,802 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>22</v>
+      </c>
+      <c r="C3">
+        <v>10000</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="G3">
+        <v>50</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>25</v>
+      </c>
+      <c r="J3">
+        <v>25</v>
+      </c>
+      <c r="K3">
+        <v>140</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>95</v>
+      </c>
+      <c r="N3">
+        <v>100</v>
+      </c>
+      <c r="O3">
+        <v>100</v>
+      </c>
+      <c r="P3">
+        <v>100</v>
+      </c>
+      <c r="Q3">
+        <v>100</v>
+      </c>
+      <c r="R3">
+        <v>100</v>
+      </c>
+      <c r="S3">
+        <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:19">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="C4">
+        <v>10000</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>50</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>25</v>
+      </c>
+      <c r="J4">
+        <v>25</v>
+      </c>
+      <c r="K4">
+        <v>140</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>95</v>
+      </c>
+      <c r="N4">
+        <v>100</v>
+      </c>
+      <c r="O4">
+        <v>100</v>
+      </c>
+      <c r="P4">
+        <v>100</v>
+      </c>
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
+        <v>100</v>
+      </c>
+      <c r="S4">
+        <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:19">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>10000</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>50</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>25</v>
+      </c>
+      <c r="J5">
+        <v>25</v>
+      </c>
+      <c r="K5">
+        <v>140</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>95</v>
+      </c>
+      <c r="N5">
+        <v>100</v>
+      </c>
+      <c r="O5">
+        <v>100</v>
+      </c>
+      <c r="P5">
+        <v>100</v>
+      </c>
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
+        <v>100</v>
+      </c>
+      <c r="S5">
+        <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>25</v>
+      </c>
+      <c r="C6">
+        <v>10000</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>50</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>25</v>
+      </c>
+      <c r="J6">
+        <v>25</v>
+      </c>
+      <c r="K6">
+        <v>140</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>95</v>
+      </c>
+      <c r="N6">
+        <v>100</v>
+      </c>
+      <c r="O6">
+        <v>100</v>
+      </c>
+      <c r="P6">
+        <v>100</v>
+      </c>
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
+        <v>100</v>
+      </c>
+      <c r="S6">
+        <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:19">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>10000</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>50</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>25</v>
+      </c>
+      <c r="J7">
+        <v>25</v>
+      </c>
+      <c r="K7">
+        <v>140</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>95</v>
+      </c>
+      <c r="N7">
+        <v>100</v>
+      </c>
+      <c r="O7">
+        <v>100</v>
+      </c>
+      <c r="P7">
+        <v>100</v>
+      </c>
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
+        <v>100</v>
+      </c>
+      <c r="S7">
+        <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:19">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>27</v>
+      </c>
+      <c r="C8">
+        <v>10000</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>50</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>25</v>
+      </c>
+      <c r="J8">
+        <v>25</v>
+      </c>
+      <c r="K8">
+        <v>140</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>95</v>
+      </c>
+      <c r="N8">
+        <v>100</v>
+      </c>
+      <c r="O8">
+        <v>100</v>
+      </c>
+      <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
+        <v>100</v>
+      </c>
+      <c r="S8">
+        <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:19">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="C9">
+        <v>10000</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9">
+        <v>50</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>25</v>
+      </c>
+      <c r="J9">
+        <v>25</v>
+      </c>
+      <c r="K9">
+        <v>140</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>95</v>
+      </c>
+      <c r="N9">
+        <v>100</v>
+      </c>
+      <c r="O9">
+        <v>100</v>
+      </c>
+      <c r="P9">
+        <v>100</v>
+      </c>
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
+        <v>100</v>
+      </c>
+      <c r="S9">
+        <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:19">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>29</v>
+      </c>
+      <c r="C10">
+        <v>10000</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>100</v>
+      </c>
+      <c r="G10">
+        <v>50</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>25</v>
+      </c>
+      <c r="J10">
+        <v>25</v>
+      </c>
+      <c r="K10">
+        <v>140</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>95</v>
+      </c>
+      <c r="N10">
+        <v>100</v>
+      </c>
+      <c r="O10">
+        <v>100</v>
+      </c>
+      <c r="P10">
+        <v>100</v>
+      </c>
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
+        <v>100</v>
+      </c>
+      <c r="S10">
+        <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:19">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="C11">
+        <v>10000</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>100</v>
+      </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="G11">
+        <v>50</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>25</v>
+      </c>
+      <c r="J11">
+        <v>25</v>
+      </c>
+      <c r="K11">
+        <v>140</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>95</v>
+      </c>
+      <c r="N11">
+        <v>100</v>
+      </c>
+      <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11">
+        <v>100</v>
+      </c>
+      <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:19">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>31</v>
+      </c>
+      <c r="C12">
+        <v>10000</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>100</v>
+      </c>
+      <c r="F12">
+        <v>100</v>
+      </c>
+      <c r="G12">
+        <v>50</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>25</v>
+      </c>
+      <c r="J12">
+        <v>25</v>
+      </c>
+      <c r="K12">
+        <v>140</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>95</v>
+      </c>
+      <c r="N12">
+        <v>100</v>
+      </c>
+      <c r="O12">
+        <v>100</v>
+      </c>
+      <c r="P12">
+        <v>100</v>
+      </c>
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
+        <v>100</v>
+      </c>
+      <c r="S12">
+        <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:19">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="C13">
+        <v>10000</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>100</v>
+      </c>
+      <c r="F13">
+        <v>100</v>
+      </c>
+      <c r="G13">
+        <v>50</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>25</v>
+      </c>
+      <c r="J13">
+        <v>25</v>
+      </c>
+      <c r="K13">
+        <v>140</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>95</v>
+      </c>
+      <c r="N13">
+        <v>100</v>
+      </c>
+      <c r="O13">
+        <v>100</v>
+      </c>
+      <c r="P13">
+        <v>100</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
+        <v>100</v>
+      </c>
+      <c r="S13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14">
+        <v>10000</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14">
+        <v>100</v>
+      </c>
+      <c r="F14">
+        <v>100</v>
+      </c>
+      <c r="G14">
+        <v>50</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>25</v>
+      </c>
+      <c r="J14">
+        <v>25</v>
+      </c>
+      <c r="K14">
+        <v>140</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>95</v>
+      </c>
+      <c r="N14">
+        <v>100</v>
+      </c>
+      <c r="O14">
+        <v>100</v>
+      </c>
+      <c r="P14">
+        <v>100</v>
+      </c>
+      <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/trunk/plan/excel/英雄属性表.xlsx
+++ b/trunk/plan/excel/英雄属性表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="8130"/>
+    <workbookView windowWidth="30585" windowHeight="8985"/>
   </bookViews>
   <sheets>
     <sheet name="HeroAttrCFG" sheetId="1" r:id="rId1"/>

--- a/trunk/plan/excel/英雄属性表.xlsx
+++ b/trunk/plan/excel/英雄属性表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30585" windowHeight="8985"/>
+    <workbookView windowWidth="27030" windowHeight="12825"/>
   </bookViews>
   <sheets>
     <sheet name="HeroAttrCFG" sheetId="1" r:id="rId1"/>
